--- a/rod_prepared_data.xlsx
+++ b/rod_prepared_data.xlsx
@@ -425,351 +425,289 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA8"/>
+  <dimension ref="A1:AS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>hotel__name</t>
+          <t>HOTEL_NAME</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>hotel__brand</t>
+          <t>HOTEL_LON</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__id__data__code_h</t>
+          <t>HOTEL_LAT</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__id__data__nom_de_l_hotel</t>
+          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__nb_de_chambres</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_1</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__bar</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__adresse_postale_2</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__restaurant</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__code_postal</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__minibar</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__ville</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salles_de_reunion</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__longitude</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salle_de_sport</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__0_page_de_connexion__sous_etape_rod__localisation_geo__data__latitude</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__piscine</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__marque</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__vitrine_refrigeree</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__nb_de_chambres</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__micro_ondes</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__contrat_type</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__fontaine_a_eau</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__proprietaire</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__machine_a_cafe</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__dom_dof</t>
+          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__bouilloire</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__1_informations_generales__sous_etape_rod__donnees_admin__data__pms</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_couples</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__bar</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_amis</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__restaurant</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_familles</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__f_b__data__minibar</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__boissons_alcoolisees</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salles_de_reunion</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sales_frais</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__salle_de_sport</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sucres_frais</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__non_f_b__data__piscine</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__epicerie_fine</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__vitrine_refrigeree</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__produits_cosmetiques</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__micro_ondes</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__articles_pour_enfants</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__fontaine_a_eau</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__pret_a_porter</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__machine_a_cafe</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__accessoires</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__2_services_equipements__sous_etape_rod__dispo_dans_le_lobby__data__bouilloire</t>
+          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__souvenirs</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_couples</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__votre_hotel_dispose_t_il_deja_d_un_corner_de_vente</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_amis</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__source_row__85</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__loisirs__data__top_1_familles</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__reception</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__boissons_alcoolisees</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__snacking_comptoir</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sales_frais</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__distributeur_auto</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__produits_sucres_frais</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__hotel_staff</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_f_b__data__epicerie_fine</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__source_row__99</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__produits_cosmetiques</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__reception</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__articles_pour_enfants</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__distributeur_auto</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__pret_a_porter</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__hotel_staff</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__accessoires</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__wifi__source_row__122</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__3_profil_de_vos_clients__sous_etape_rod__besoins_de_vos_clients_non_f_b__data__souvenirs</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__internet_filaire_prise_rj45__source_row__123</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__corner_de_vente_actuel__data__votre_hotel_dispose_t_il_deja_d_un_corner_de_vente</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__alimentation_electrique__source_row__124</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__liste_des_produits_f_b__source_row__85</t>
+          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__videosurveillance__source_row__125</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__reception</t>
+          <t>IBIS BUDGET</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__snacking_comptoir</t>
+          <t>IBIS STYLES</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__distributeur_auto</t>
+          <t>MERCURE</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_f_b__data__hotel_staff</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__liste_des_produits_non_f_b__source_row__99</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__reception</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__distributeur_auto</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__votre_corner_actuel_offre_non_f_b__data__hotel_staff</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__wifi__source_row__122</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__internet_filaire_prise_rj45__source_row__123</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__alimentation_electrique__source_row__124</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>etape_rod__4_informations_corner__sous_etape_rod__equipements_disponibles__data__videosurveillance__source_row__125</t>
+          <t>NOVOTEL</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NICE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IBIS BUDGET</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>H2075</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>IBIS BUDGET NICE CALIFORNIE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>58-60 AVENUE DE LA CALIFORNIE</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Ibis budget Nice</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7.240512</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.689186</v>
+      </c>
+      <c r="D2" t="n">
+        <v>129</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>6200</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>NICE</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>7.240512</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>43.689186</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>IBIS BUDGET</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>129</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>FRANCHISE</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>FAMILLE FARINES</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Marion BOROT</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>FOLS</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -778,16 +716,16 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -799,10 +737,10 @@
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
         <v>1</v>
@@ -817,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -829,144 +767,98 @@
         <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STRASBOURG</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IBIS BUDGET</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HB6A3</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>IBIS BUDGET STRASBOURG REPUBLIQUE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>23A RUE OBERLIN</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Ibis budget Strasbourg Centre République</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7.754599</v>
+      </c>
+      <c r="C3" t="n">
+        <v>48.591522</v>
+      </c>
+      <c r="D3" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>67000</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>STRASBOURG</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>7.754599</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>48.591522</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>IBIS BUDGET</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>97</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>FRANCHISE</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>MILLION - CHOREIN</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Christophe RUQUEBOEUCHE</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>OPERA</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -978,25 +870,25 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
         <v>1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>1</v>
@@ -1008,19 +900,19 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
@@ -1032,126 +924,80 @@
         <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PARIS CDG</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IBIS STYLES</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>H0815</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
           <t>IBIS STYLES ROISSY CDG</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2 AVENUE HEINZ GLOOR</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" t="n">
+        <v>2.519843</v>
+      </c>
+      <c r="C4" t="n">
+        <v>49.006733</v>
+      </c>
+      <c r="D4" t="n">
+        <v>309</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>95700</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ROISSY</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2.519843</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>49.006733</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>IBIS STYLES</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>309</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>FRANCHISE</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>FERRE HOTELS</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Sophie CHOLLON</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>FOLS</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1160,22 +1006,22 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>1</v>
@@ -1190,171 +1036,125 @@
         <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MEGEVE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NOVOTEL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>HB5I0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NOVOTEL MEGEVE MONT BLANC</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1306 ROUTE NATIONALE</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>LE DOMAINE DE MEZTIVA</t>
-        </is>
+          <t>Novotel Megève Mont-Blanc</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6.6190552711</v>
+      </c>
+      <c r="C5" t="n">
+        <v>45.8591651916</v>
+      </c>
+      <c r="D5" t="n">
+        <v>572</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>74120</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>MEGEVE</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6190552711</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>45.8591651916</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>NOVOTEL</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>572</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>FRANCHISE</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>FAMILLE DELETTRE</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Bello DIALLO</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>FOLS</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1366,13 +1166,13 @@
         <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
         <v>1</v>
@@ -1381,16 +1181,16 @@
         <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -1399,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
@@ -1409,116 +1209,70 @@
       </c>
       <c r="AS5" t="n">
         <v>1</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TOUR EIFFEL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NOVOTEL</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>H3546</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NOVOTEL PARIS CENTRE TOUR EIFFEL</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>61 QUAI DE GRENELLE</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Novotel Paris Tour Eiffel</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.282836</v>
+      </c>
+      <c r="C6" t="n">
+        <v>48.849778</v>
+      </c>
+      <c r="D6" t="n">
+        <v>764</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>75015</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PARIS</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>36</v>
       </c>
       <c r="I6" t="n">
-        <v>2.282836</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>48.849778</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>NOVOTEL</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>764</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>MANAGÉ</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>ACCORINVEST FRANCE</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Philippe JAUSSELY</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>OPERA</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
@@ -1527,10 +1281,10 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
@@ -1539,16 +1293,16 @@
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1557,31 +1311,31 @@
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
         <v>1</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -1590,117 +1344,71 @@
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MONTMARTRE</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MERCURE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>H0373</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MERCURE MONTMARTRE SACRE COEUR</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>3  RUE CAULAINCOURT</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Mercure Paris Montmartre Sacré-Cœur</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.329923</v>
+      </c>
+      <c r="C7" t="n">
+        <v>48.885048</v>
+      </c>
+      <c r="D7" t="n">
+        <v>305</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>75018</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PARIS</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>2.329923</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>48.885048</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>MERCURE</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>305</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>MANAGÉ</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>ACCORINVEST FRANCE</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Thibault FREMONT</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>OPERA</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1709,204 +1417,158 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="n">
         <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>1</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BOULOGNE</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MERCURE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>H6188</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
           <t>MERCURE PARIS BOULOGNE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>37 PLACE RENÉ CLAIR</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" t="n">
+        <v>2.256274</v>
+      </c>
+      <c r="C8" t="n">
+        <v>48.833827</v>
+      </c>
+      <c r="D8" t="n">
+        <v>191</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>92100</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>BOULOGNE-BILLANCOURT</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>2.256274</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>48.833827</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>MERCURE</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>191</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>FRANCHISE</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>GROUPE COVIVIO</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Hubert VANQUATHEM</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>OPERA</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1915,16 +1577,16 @@
         <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>1</v>
@@ -1933,60 +1595,36 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
         <v>0</v>
       </c>
     </row>
